--- a/AdditionalData/Tables/Megalithic blocks.xlsx
+++ b/AdditionalData/Tables/Megalithic blocks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="podrías hacer un resumen de los" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -167,16 +167,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -373,91 +377,91 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="69.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="69.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>18</v>
       </c>
     </row>
